--- a/kaynak/KULE-alerjen-kontrol.xlsx
+++ b/kaynak/KULE-alerjen-kontrol.xlsx
@@ -10208,8 +10208,16 @@
       <c r="E124" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="F124" s="4" t="inlineStr"/>
-      <c r="G124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>Gazlı içecek</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>Carbonated soft drink</t>
+        </is>
+      </c>
       <c r="H124" s="5" t="inlineStr"/>
       <c r="I124" s="5" t="inlineStr"/>
       <c r="J124" s="5" t="inlineStr"/>
@@ -10266,8 +10274,16 @@
       <c r="E125" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="F125" s="4" t="inlineStr"/>
-      <c r="G125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>Şekersiz gazlı içecek</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>Sugar-free carbonated soft drink</t>
+        </is>
+      </c>
       <c r="H125" s="5" t="inlineStr"/>
       <c r="I125" s="5" t="inlineStr"/>
       <c r="J125" s="5" t="inlineStr"/>
@@ -10324,8 +10340,16 @@
       <c r="E126" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="F126" s="4" t="inlineStr"/>
-      <c r="G126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>Limon aromalı gazlı içecek</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>Lemon-lime soft drink</t>
+        </is>
+      </c>
       <c r="H126" s="5" t="inlineStr"/>
       <c r="I126" s="5" t="inlineStr"/>
       <c r="J126" s="5" t="inlineStr"/>
@@ -10382,8 +10406,16 @@
       <c r="E127" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="F127" s="4" t="inlineStr"/>
-      <c r="G127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>Portakal aromalı gazlı içecek</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>Orange soft drink</t>
+        </is>
+      </c>
       <c r="H127" s="5" t="inlineStr"/>
       <c r="I127" s="5" t="inlineStr"/>
       <c r="J127" s="5" t="inlineStr"/>
@@ -10844,8 +10876,16 @@
       <c r="E134" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="F134" s="4" t="inlineStr"/>
-      <c r="G134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>Maden suyu</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>Sparkling mineral water</t>
+        </is>
+      </c>
       <c r="H134" s="5" t="inlineStr"/>
       <c r="I134" s="5" t="inlineStr"/>
       <c r="J134" s="5" t="inlineStr"/>
@@ -10902,8 +10942,16 @@
       <c r="E135" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="F135" s="4" t="inlineStr"/>
-      <c r="G135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>Meyve aromalı maden suyu</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>Fruit-flavoured mineral water</t>
+        </is>
+      </c>
       <c r="H135" s="5" t="inlineStr"/>
       <c r="I135" s="5" t="inlineStr"/>
       <c r="J135" s="5" t="inlineStr"/>
@@ -10962,12 +11010,12 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>Limon, su, şeker, nane</t>
+          <t>Limon, su, şeker</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>Lemon, water, sugar, mint</t>
+          <t>Lemon, water, sugar</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr"/>

--- a/kaynak/KULE-alerjen-kontrol.xlsx
+++ b/kaynak/KULE-alerjen-kontrol.xlsx
@@ -13834,7 +13834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -14252,38 +14252,74 @@
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Sosis Box</t>
+          <t xml:space="preserve">  TÜM İÇECEKLER (05.10.2026)</t>
         </is>
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>'8 adet ızgara sosis' -&gt; '8 adet sosis'.</t>
+          <t>İçecekler bölümünün TAMAMINDA (76 ürün) ve Dondurma (1/3 Top)'ta içindekiler artık menüde GÖSTERİLMİYOR. ÖNEMLİ: alerjenler gösterilmeye devam ediyor — sütlü kahveler, milkshake'ler, ayran ve dondurma hâlâ SÜT uyarısı veriyor (mevzuat gereği kaldırmadım; kaldırılsın isterseniz söyleyin). İçindekiler verisi arka planda duruyor, alerjen oradan türetiliyor.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Limonata</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>Nane çıkarıldı: limon, su, şeker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gizleme nasıl değişir</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>kaynak/build.js içindeki IHIDE_SECTIONS (bölüm id'si) ve IHIDE_ITEMS (ürün adı) listelerine ekleyip çıkararak. Cappy / Fuse Tea zaten içecek bölümünde olduğu için onlar da gizli.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sosis Box</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>'8 adet ızgara sosis' -&gt; '8 adet sosis'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Big Combo Mix</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>Sigara böreğinin içindekileri yazıldı (yufka, beyaz peynir, maydanoz, soda, tuz) — SÜT artık beyaz peynirden türüyor.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr"/>
-      <c r="B40" s="16" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr"/>
+      <c r="B43" s="16" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
         <is>
           <t>BESİN DEĞERLERİ</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>Tatlılar bölümündeki Lupin ürünleri üreticinin 100 g beyanı x ürün gramajıdır. DİĞER TÜM ürünlerin kcal / protein / yağ / karbonhidrat değerleri TAHMİNDİR — diyetisyen doğrulaması gerekir.</t>
         </is>
